--- a/docs/培训/OpenWorker培训/04-备件盘点/备件台账.xlsx
+++ b/docs/培训/OpenWorker培训/04-备件盘点/备件台账.xlsx
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="3">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="4">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="5">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="6">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="7">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="8">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="9">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46220</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="10">
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="11">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46218</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="12">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="13">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="14">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="15">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="16">
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46211</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="17">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="18">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="19">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="20">
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46226</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="21">
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="22">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="23">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="24">
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46220</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="25">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="26">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46218</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="27">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="28">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="29">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="30">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="31">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>46211</v>
+        <v>46217</v>
       </c>
     </row>
   </sheetData>
